--- a/ВИМ-АПС_кабель_по_КЖ.xlsx
+++ b/ВИМ-АПС_кабель_по_КЖ.xlsx
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493 м</t>
+          <t xml:space="preserve">2206 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">38 м</t>
+          <t xml:space="preserve">5515 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G25" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 уп.</t>
+          <t xml:space="preserve">4 уп.</t>
         </is>
       </c>
       <c r="H25" s="97" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G26" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 уп.</t>
+          <t xml:space="preserve">4 уп.</t>
         </is>
       </c>
       <c r="H26" s="97" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3179 м</t>
+          <t xml:space="preserve">2987 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">81 м</t>
+          <t xml:space="preserve">7468 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025 м</t>
+          <t xml:space="preserve">2947 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1536 м</t>
+          <t xml:space="preserve">1443 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">39 м</t>
+          <t xml:space="preserve">3608 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453 м</t>
+          <t xml:space="preserve">1423 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249 м</t>
+          <t xml:space="preserve">3053 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">82 м</t>
+          <t xml:space="preserve">10173 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3949 м</t>
+          <t xml:space="preserve">4014 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187 м</t>
+          <t xml:space="preserve">1115 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 м</t>
+          <t xml:space="preserve">2788 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124 м</t>
+          <t xml:space="preserve">1100 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190 м</t>
+          <t xml:space="preserve">2058 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">57 м</t>
+          <t xml:space="preserve">7495 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882 м</t>
+          <t xml:space="preserve">2958 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G23" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">467 м</t>
+          <t xml:space="preserve">439 м</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="G24" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 м</t>
+          <t xml:space="preserve">1098 шт.</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">442 м</t>
+          <t xml:space="preserve">433 м</t>
         </is>
       </c>
       <c r="H27" s="97" t="inlineStr">
